--- a/MCU_MODULES.xlsx
+++ b/MCU_MODULES.xlsx
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>128 KB internal + 8 MB QSPI (BOOT_QSPI)</t>
+          <t>128 KB internal + 8 MB QSPI (runs BOOT_NONE — internal flash, no bootloader)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>Stereo L/R, with output voicing: DC-block → ~14.5 kHz LPF → soft clamp</t>
+          <t>Stereo L/R, with output voicing: DC-block → soft clamp (the Seed build's ~14.5 kHz LPF is disabled on the Patch SM)</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
-          <t>daisy_multifx_oled/README.md</t>
+          <t>daisy_multifx_oled/README.md; daisy_multifx_oled/Makefile (APP_TYPE)</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Electrosmith Daisy — STM32H750</t>
+          <t>Electrosmith Daisy Seed 2 DFM — STM32H750</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Internal + QSPI flash; MIT-licensed SDK</t>
+          <t>16 MB flash (per maker); MIT-licensed SDK (hermetic-modular/alchemy-sdk)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>USB-C (MIDI)</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>USB-C MIDI</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -3255,22 +3255,22 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>Not recorded in the repos</t>
+          <t>Stereo L/R, up to 96 kHz / 24-bit</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>Not recorded in the repos</t>
+          <t>Stereo L/R, up to 96 kHz / 24-bit</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>102 addressable LEDs</t>
+          <t>No screen — 102 addressable RGB LEDs</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Not recorded in the repos</t>
+          <t>6 pots, 3 buttons; rear SPI / I2C expansion header</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="U30" s="7" t="inlineStr">
         <is>
-          <t>MODULES.md</t>
+          <t>MODULES.md; hermeticmodular.com/modules/alchemy-lab and the Synth Anatomy launch article (2026-07), checked 2026-09-24</t>
         </is>
       </c>
     </row>
